--- a/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 20,92</t>
+          <t>-12,73; 21,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 12,51</t>
+          <t>-27,48; 12,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 16,66</t>
+          <t>-29,89; 15,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 35,43</t>
+          <t>-15,9; 36,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 21,95</t>
+          <t>-35,34; 21,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 26,52</t>
+          <t>-39,24; 25,63</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 10,58</t>
+          <t>-16,08; 10,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 21,33</t>
+          <t>-13,36; 19,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 1,31</t>
+          <t>-34,05; 0,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 15,61</t>
+          <t>-20,81; 15,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 41,44</t>
+          <t>-18,11; 37,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,63; 1,2</t>
+          <t>-49,29; 0,91</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 25,98</t>
+          <t>-17,81; 26,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 45,87</t>
+          <t>6,75; 46,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 12,21</t>
+          <t>-25,33; 13,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 74,3</t>
+          <t>-30,84; 75,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 163,67</t>
+          <t>14,29; 182,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 25,14</t>
+          <t>-37,97; 28,44</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 53,8</t>
+          <t>10,52; 52,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 19,11</t>
+          <t>-30,72; 19,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 43,97</t>
+          <t>-9,93; 45,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,05; 214,1</t>
+          <t>20,14; 201,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 51,46</t>
+          <t>-51,8; 53,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 103,88</t>
+          <t>-18,11; 116,36</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 14,36</t>
+          <t>-3,93; 12,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 17,0</t>
+          <t>-4,45; 15,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 18,19</t>
+          <t>-12,3; 18,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 25,25</t>
+          <t>-6,04; 22,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 33,29</t>
+          <t>-7,43; 30,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 34,17</t>
+          <t>-20,25; 33,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 21,6</t>
+          <t>-13,08; 21,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 12,74</t>
+          <t>-27,49; 12,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 15,11</t>
+          <t>-27,92; 16,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 36,66</t>
+          <t>-17,11; 35,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 21,64</t>
+          <t>-35,07; 21,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 25,63</t>
+          <t>-36,16; 27,01</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 10,44</t>
+          <t>-15,3; 11,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 19,78</t>
+          <t>-12,39; 21,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 0,81</t>
+          <t>-35,63; 0,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 15,92</t>
+          <t>-19,4; 18,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 37,79</t>
+          <t>-17,91; 38,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,29; 0,91</t>
+          <t>-50,8; 0,02</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 26,26</t>
+          <t>-19,86; 24,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 46,27</t>
+          <t>6,06; 44,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 13,91</t>
+          <t>-22,62; 12,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 75,3</t>
+          <t>-34,19; 64,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 182,76</t>
+          <t>11,63; 155,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 28,44</t>
+          <t>-34,48; 28,37</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,52; 52,15</t>
+          <t>8,63; 50,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 19,66</t>
+          <t>-30,54; 17,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 45,84</t>
+          <t>-10,22; 43,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 201,09</t>
+          <t>17,19; 204,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 53,81</t>
+          <t>-52,29; 48,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 116,36</t>
+          <t>-18,85; 102,93</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 12,75</t>
+          <t>-4,01; 14,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,19</t>
+          <t>-3,74; 16,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 18,16</t>
+          <t>-12,88; 17,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 22,05</t>
+          <t>-5,81; 24,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 30,38</t>
+          <t>-6,11; 33,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 33,75</t>
+          <t>-21,41; 34,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,78</t>
+          <t>-8,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-8,29%</t>
+          <t>-12,15%</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 21,17</t>
+          <t>-13,24; 20,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 12,54</t>
+          <t>-28,82; 12,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 16,77</t>
+          <t>-34,87; 13,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 35,46</t>
+          <t>-16,8; 35,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 21,15</t>
+          <t>-36,23; 21,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 27,01</t>
+          <t>-45,07; 19,62</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-16,93</t>
+          <t>-17,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-26,78%</t>
+          <t>-25,8%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 11,52</t>
+          <t>-18,31; 10,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 21,37</t>
+          <t>-11,74; 21,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 0,11</t>
+          <t>-35,17; 0,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 18,27</t>
+          <t>-22,71; 15,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 38,0</t>
+          <t>-16,5; 41,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 0,02</t>
+          <t>-47,51; 0,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,74</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-9,82%</t>
+          <t>-11,66%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 24,01</t>
+          <t>-19,29; 25,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 44,55</t>
+          <t>6,32; 45,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 12,89</t>
+          <t>-25,65; 11,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 64,18</t>
+          <t>-33,51; 74,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,63; 155,04</t>
+          <t>14,13; 163,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 28,37</t>
+          <t>-38,16; 22,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,92</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 50,94</t>
+          <t>6,05; 53,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 17,87</t>
+          <t>-30,55; 19,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 43,84</t>
+          <t>-10,1; 23,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 204,32</t>
+          <t>13,05; 214,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 48,29</t>
+          <t>-51,39; 51,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 102,93</t>
+          <t>-16,72; 54,72</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,85%</t>
+          <t>-8,36%</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 14,34</t>
+          <t>-4,42; 14,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 16,58</t>
+          <t>-3,41; 17,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 17,95</t>
+          <t>-15,53; 5,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 24,75</t>
+          <t>-6,48; 25,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 33,29</t>
+          <t>-5,76; 33,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 34,33</t>
+          <t>-23,62; 9,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,38</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,33</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-8,69</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-10,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-12,15%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.915734031797529</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.0811444776308401</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6490906440726862</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-7.581636219489191</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1193433943715298</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.004444524788475367</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.04809700995633419</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3072551117035768</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,24; 20,92</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-28,82; 12,51</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-34,87; 13,17</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-16,8; 35,43</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-36,23; 21,95</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-45,07; 19,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.842595935347298</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.684145800501346</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.062455826466113</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-18.56728769007285</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2368169331569858</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3466156590136035</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4255308488069299</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6045433797588243</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.74103281357362</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.976008946965519</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.714522805463096</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.17932783143679</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.5678224755194015</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.4964417003092648</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.5580966905215753</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1839386881892056</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-17,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-25,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-18,31; 10,58</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,74; 21,33</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-35,17; 0,56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-22,71; 15,61</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-16,5; 41,44</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-47,51; 0,94</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.012807238972945</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.265658164855219</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.915093414324521</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.586135026706924</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1500233384936757</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1244069339109896</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2761586244070733</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2065067290595393</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26,6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-11,66%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.159368456967918</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.643835221903992</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.281981930387859</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.37656201782951</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3716643536259671</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3714671305157769</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1668915781365861</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4891481000826793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-19,29; 25,98</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,32; 45,87</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-25,65; 11,19</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-33,51; 74,3</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,13; 163,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-38,16; 22,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.496116667600091</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.465279858410554</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.571051261625551</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.699861794342191</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1397361366182242</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2179262797277396</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.9007431272121971</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.289660064122454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32,45</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-12,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.7807700105622595</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7924589866558474</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.623552955267483</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.590665240504358</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.04629580739918413</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.09096879759262685</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.8181762107793108</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1221643813804252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6,05; 53,8</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-30,55; 19,11</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-10,1; 23,38</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,05; 214,1</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-51,39; 51,46</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-16,72; 54,72</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.282960721185969</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.773968241972661</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8682335016042936</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.644321893942324</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3049888716198129</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4121314833859656</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.07789317248881027</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4651997726516103</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.315164983775549</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.79686834473523</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.69034624733375</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.930099479196989</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6258983220025509</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.023864732337713</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.258027726998917</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3978019115251828</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.403981728544886</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.908215495585814</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.9459692629793861</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.297848589584275</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1778460488309129</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.107739464671203</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1493899539357703</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.02691398808153784</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-9.665142585730299</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.224975771010233</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.258213534745548</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.443182052421736</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4174723173023458</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.1363720935904198</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6160775876197867</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3434258401106501</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.684073448057579</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.46238732599713</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.606244751247309</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.572737229647735</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1887135357268869</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.998808846007482</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.001372291790037</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.6316134883791532</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,22</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,98</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-8,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 14,36</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,41; 17,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-15,53; 5,23</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-6,48; 25,25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,76; 33,29</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-23,62; 9,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.514437309679839</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.7322723599786307</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.977215733059039</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.601321831781365</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.07604862347984856</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.05565355449221963</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2166425668212398</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1142263238015739</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.162714120891358</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.144569173446441</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.4410158789971705</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.628181376583795</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2338327333113071</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1511101729516584</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.05084802875635521</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2915416358481522</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.551920647295891</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.855364185873528</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.674636737829599</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.696051921258303</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.08308181202454276</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.32375618310732</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.592219890013166</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1435783790311292</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
